--- a/crates/xlstream-eval/tests/fixtures/text/find_search.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/text/find_search.xlsx
@@ -20,21 +20,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">text</t>
   </si>
   <si>
-    <t xml:space="preserve">find</t>
-  </si>
-  <si>
-    <t xml:space="preserve">search</t>
+    <t xml:space="preserve">find_l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_L</t>
   </si>
   <si>
     <t xml:space="preserve">substitute</t>
   </si>
   <si>
-    <t xml:space="preserve">replace</t>
+    <t xml:space="preserve">replace_1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">find_missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_case</t>
   </si>
   <si>
     <t xml:space="preserve">hello</t>
@@ -43,28 +49,28 @@
     <t xml:space="preserve">WORLD</t>
   </si>
   <si>
-    <t xml:space="preserve">  spaces  here  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">abc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProPer Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num123</t>
+    <t xml:space="preserve">abcabc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hello World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no match here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPPER lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12345</t>
   </si>
   <si>
     <t xml:space="preserve">foo bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
   </si>
 </sst>
 </file>
@@ -337,7 +343,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -356,10 +362,16 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A2),0)</f>
@@ -377,10 +389,18 @@
         <f aca="false">REPLACE(A2,1,1,"X")</f>
         <v>Xello</v>
       </c>
+      <c r="F2" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A2),0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A3),0)</f>
@@ -398,10 +418,18 @@
         <f aca="false">REPLACE(A3,1,1,"X")</f>
         <v>XORLD</v>
       </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A3),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A3),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A4),0)</f>
@@ -413,16 +441,24 @@
       </c>
       <c r="D4" s="0" t="str">
         <f aca="false">SUBSTITUTE(A4,"o","0")</f>
-        <v>  spaces  here  </v>
+        <v>abcabc</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">REPLACE(A4,1,1,"X")</f>
-        <v>X spaces  here  </v>
+        <v>Xbcabc</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A4),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A5),0)</f>
@@ -434,37 +470,53 @@
       </c>
       <c r="D5" s="0" t="str">
         <f aca="false">SUBSTITUTE(A5,"o","0")</f>
-        <v>abc</v>
+        <v>test123</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">REPLACE(A5,1,1,"X")</f>
-        <v>Xbc</v>
+        <v>Xest123</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A5),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A5),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A6),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">IFERROR(SEARCH("L",A6),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0" t="str">
         <f aca="false">SUBSTITUTE(A6,"o","0")</f>
-        <v>sh0rt</v>
+        <v>Hell0 W0rld</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">REPLACE(A6,1,1,"X")</f>
-        <v>Xhort</v>
+        <v>Xello World</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A6),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A6),0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A7),0)</f>
@@ -476,37 +528,53 @@
       </c>
       <c r="D7" s="0" t="str">
         <f aca="false">SUBSTITUTE(A7,"o","0")</f>
-        <v>test</v>
+        <v>n0 match here</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">REPLACE(A7,1,1,"X")</f>
-        <v>Xest</v>
+        <v>Xo match here</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A7),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A8),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">IFERROR(SEARCH("L",A8),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="0" t="str">
         <f aca="false">SUBSTITUTE(A8,"o","0")</f>
-        <v>Pr0Per Case</v>
+        <v>UPPER l0wer</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">REPLACE(A8,1,1,"X")</f>
-        <v>XroPer Case</v>
+        <v>XPPER lower</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A8),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A8),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A9),0)</f>
@@ -518,16 +586,24 @@
       </c>
       <c r="D9" s="0" t="str">
         <f aca="false">SUBSTITUTE(A9,"o","0")</f>
-        <v>num123</v>
+        <v>aaa</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">REPLACE(A9,1,1,"X")</f>
-        <v>Xum123</v>
+        <v>Xaa</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A9),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A9),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A10),0)</f>
@@ -539,16 +615,24 @@
       </c>
       <c r="D10" s="0" t="str">
         <f aca="false">SUBSTITUTE(A10,"o","0")</f>
-        <v>f00 bar</v>
+        <v>12345</v>
       </c>
       <c r="E10" s="0" t="str">
         <f aca="false">REPLACE(A10,1,1,"X")</f>
-        <v>Xoo bar</v>
+        <v>X2345</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A10),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A10),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">IFERROR(FIND("l",A11),0)</f>
@@ -560,11 +644,19 @@
       </c>
       <c r="D11" s="0" t="str">
         <f aca="false">SUBSTITUTE(A11,"o","0")</f>
-        <v>x</v>
+        <v>f00 bar</v>
       </c>
       <c r="E11" s="0" t="str">
         <f aca="false">REPLACE(A11,1,1,"X")</f>
-        <v>X</v>
+        <v>Xoo bar</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">IFERROR(FIND("zzz",A11),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <f aca="false">IFERROR(SEARCH("hello",A11),0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
